--- a/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_raw.xlsx
+++ b/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_raw.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/vorlesungen/Allgemeine Daten/covariate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CFEC55-7965-A149-8A7D-A017E03B1CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E5B0A6-F656-C547-B9C3-9EA8CAD51EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4900" yWindow="3020" windowWidth="36000" windowHeight="20620" xr2:uid="{A5B12C49-1460-7B46-AA19-811389EE84C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
   <si>
     <t>fid</t>
   </si>
@@ -67,13 +67,16 @@
   <si>
     <t>bodyweight</t>
   </si>
+  <si>
+    <t>mean</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -106,7 +109,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -259,22 +262,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>30.200000000000003</c:v>
+                  <c:v>26.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.200000000000003</c:v>
+                  <c:v>28.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>27.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24.4</c:v>
+                  <c:v>21.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>29.200000000000003</c:v>
+                  <c:v>22.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32.200000000000003</c:v>
+                  <c:v>29.3</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>24.6</c:v>
@@ -310,7 +313,7 @@
                   <c:v>35.1</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>32.4</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>37.1</c:v>
@@ -829,67 +832,67 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>7.31646909511724</c:v>
+                  <c:v>8.5913968960289822</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.7218827786121809</c:v>
+                  <c:v>8.8163872986800307</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.0030834451737736</c:v>
+                  <c:v>4.0986279129456946</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.7373257292292248</c:v>
+                  <c:v>6.3121984072961492</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.2317284424398309</c:v>
+                  <c:v>4.6553029875884855</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5552895628505508</c:v>
+                  <c:v>3.8978603936994363</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.1154018411183682</c:v>
+                  <c:v>1.7644101439598745</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.0783389461155526</c:v>
+                  <c:v>8.540499169321178</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.9269373449618037</c:v>
+                  <c:v>5.1848323299896935</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.820258898030108</c:v>
+                  <c:v>9.160407229991014</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.794356996267517</c:v>
+                  <c:v>9.8355690549857471</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13.085290037842814</c:v>
+                  <c:v>9.8680058184757993</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.5542382804923562</c:v>
+                  <c:v>11.927912348853017</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>10.165636019884383</c:v>
+                  <c:v>7.6725475000825263</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14.884347488358706</c:v>
+                  <c:v>14.656159059412463</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>16.448102799094741</c:v>
+                  <c:v>10.551558005405006</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>15.69630373126359</c:v>
+                  <c:v>11.548986677155275</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>16.177382142751551</c:v>
+                  <c:v>14.25617181434581</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>16.07878941680298</c:v>
+                  <c:v>15.65322685223035</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>17.471696072041642</c:v>
+                  <c:v>14.801295568464589</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>13.679708813525982</c:v>
+                  <c:v>13.592116001964307</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2313,16 +2316,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>280147</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>339911</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>100107</xdr:rowOff>
+      <xdr:rowOff>115048</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>705970</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>765735</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>19424</xdr:rowOff>
+      <xdr:rowOff>34365</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2349,16 +2352,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>287620</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>324972</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>107577</xdr:rowOff>
+      <xdr:rowOff>129989</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>713443</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>750796</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>26895</xdr:rowOff>
+      <xdr:rowOff>49307</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2703,10 +2706,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E49B87-C84A-2142-A99F-5E2EBBD232E0}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2725,8 +2728,11 @@
       <c r="H1" t="s">
         <v>3</v>
       </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2738,17 +2744,21 @@
       </c>
       <c r="D2" s="1">
         <f ca="1">2+1.2*B2+_xlfn.NORM.INV(RAND(),0,2)</f>
-        <v>7.31646909511724</v>
+        <v>8.5913968960289822</v>
       </c>
       <c r="E2">
-        <v>30.200000000000003</v>
+        <v>26.4</v>
       </c>
       <c r="H2">
         <f>_xlfn.STDEV.S(E2:E8)</f>
-        <v>3.0873011792548812</v>
+        <v>3.0873011792548648</v>
+      </c>
+      <c r="I2">
+        <f>AVERAGE(E2:E8)</f>
+        <v>25.614285714285717</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2760,17 +2770,21 @@
       </c>
       <c r="D3" s="1">
         <f t="shared" ref="D3:D22" ca="1" si="0">2+1.2*B3+_xlfn.NORM.INV(RAND(),0,2)</f>
-        <v>5.7218827786121809</v>
+        <v>8.8163872986800307</v>
       </c>
       <c r="E3">
-        <v>31.200000000000003</v>
+        <v>28.1</v>
       </c>
       <c r="H3">
         <f>_xlfn.STDEV.S(E9:E15)</f>
         <v>2.1187372699434817</v>
       </c>
+      <c r="I3">
+        <f>AVERAGE(E9:E15)</f>
+        <v>15.328571428571431</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2782,17 +2796,21 @@
       </c>
       <c r="D4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7.0030834451737736</v>
+        <v>4.0986279129456946</v>
       </c>
       <c r="E4">
         <v>27.6</v>
       </c>
       <c r="H4">
         <f>_xlfn.STDEV.S(E16:E22)</f>
-        <v>5.0164491330783116</v>
+        <v>5.219651511812045</v>
+      </c>
+      <c r="I4">
+        <f>AVERAGE(E16:E22)</f>
+        <v>31.485714285714288</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2804,13 +2822,13 @@
       </c>
       <c r="D5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.7373257292292248</v>
+        <v>6.3121984072961492</v>
       </c>
       <c r="E5">
-        <v>24.4</v>
+        <v>21.2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2822,13 +2840,13 @@
       </c>
       <c r="D6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.2317284424398309</v>
+        <v>4.6553029875884855</v>
       </c>
       <c r="E6">
-        <v>29.200000000000003</v>
+        <v>22.1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2840,13 +2858,13 @@
       </c>
       <c r="D7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.5552895628505508</v>
+        <v>3.8978603936994363</v>
       </c>
       <c r="E7">
-        <v>32.200000000000003</v>
+        <v>29.3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2858,13 +2876,13 @@
       </c>
       <c r="D8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.1154018411183682</v>
+        <v>1.7644101439598745</v>
       </c>
       <c r="E8">
         <v>24.6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2876,13 +2894,13 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.0783389461155526</v>
+        <v>8.540499169321178</v>
       </c>
       <c r="E9">
         <v>14.2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2894,13 +2912,13 @@
       </c>
       <c r="D10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.9269373449618037</v>
+        <v>5.1848323299896935</v>
       </c>
       <c r="E10">
         <v>17.3</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2912,13 +2930,13 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.820258898030108</v>
+        <v>9.160407229991014</v>
       </c>
       <c r="E11">
         <v>13.100000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2930,13 +2948,13 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.794356996267517</v>
+        <v>9.8355690549857471</v>
       </c>
       <c r="E12">
         <v>14.100000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2948,13 +2966,13 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.085290037842814</v>
+        <v>9.8680058184757993</v>
       </c>
       <c r="E13">
         <v>14.3</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2966,13 +2984,13 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.5542382804923562</v>
+        <v>11.927912348853017</v>
       </c>
       <c r="E14">
         <v>15.2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2984,13 +3002,13 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.165636019884383</v>
+        <v>7.6725475000825263</v>
       </c>
       <c r="E15">
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3002,7 +3020,7 @@
       </c>
       <c r="D16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.884347488358706</v>
+        <v>14.656159059412463</v>
       </c>
       <c r="E16">
         <v>27.6</v>
@@ -3020,7 +3038,7 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.448102799094741</v>
+        <v>10.551558005405006</v>
       </c>
       <c r="E17">
         <v>22.2</v>
@@ -3038,7 +3056,7 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.69630373126359</v>
+        <v>11.548986677155275</v>
       </c>
       <c r="E18">
         <v>35.1</v>
@@ -3056,10 +3074,10 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.177382142751551</v>
+        <v>14.25617181434581</v>
       </c>
       <c r="E19">
-        <v>32.4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -3074,7 +3092,7 @@
       </c>
       <c r="D20" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.07878941680298</v>
+        <v>15.65322685223035</v>
       </c>
       <c r="E20">
         <v>37.1</v>
@@ -3092,7 +3110,7 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.471696072041642</v>
+        <v>14.801295568464589</v>
       </c>
       <c r="E21">
         <v>33.299999999999997</v>
@@ -3110,7 +3128,7 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.679708813525982</v>
+        <v>13.592116001964307</v>
       </c>
       <c r="E22">
         <v>30.1</v>

--- a/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_raw.xlsx
+++ b/Allgemeine Daten/covariate/flea_jumplength_bloodmeal_raw.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/vorlesungen/Allgemeine Daten/covariate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28CFEC55-7965-A149-8A7D-A017E03B1CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{028830E0-1195-874D-9631-0AC530C8CF13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4900" yWindow="3020" windowWidth="36000" windowHeight="20620" xr2:uid="{A5B12C49-1460-7B46-AA19-811389EE84C0}"/>
+    <workbookView xWindow="2400" yWindow="600" windowWidth="36000" windowHeight="19960" xr2:uid="{A5B12C49-1460-7B46-AA19-811389EE84C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
   <si>
     <t>fid</t>
   </si>
@@ -67,13 +67,16 @@
   <si>
     <t>bodyweight</t>
   </si>
+  <si>
+    <t>mean</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -106,7 +109,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -259,31 +262,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>30.200000000000003</c:v>
+                  <c:v>27.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31.200000000000003</c:v>
+                  <c:v>28.200000000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>27.6</c:v>
+                  <c:v>24.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>24.4</c:v>
+                  <c:v>21.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>26.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>29.200000000000003</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>32.200000000000003</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>24.6</c:v>
+                  <c:v>21.6</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>14.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>17.3</c:v>
+                  <c:v>15.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>13.100000000000001</c:v>
@@ -829,67 +832,67 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>7.31646909511724</c:v>
+                  <c:v>4.3746426426433738</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.7218827786121809</c:v>
+                  <c:v>5.5008606877370481</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.0030834451737736</c:v>
+                  <c:v>6.728532060884449</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.7373257292292248</c:v>
+                  <c:v>7.4244846225858225</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.2317284424398309</c:v>
+                  <c:v>7.2868256008981298</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.5552895628505508</c:v>
+                  <c:v>1.0148031525997094</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.1154018411183682</c:v>
+                  <c:v>6.3401554116243615</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.0783389461155526</c:v>
+                  <c:v>8.8722619994024718</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.9269373449618037</c:v>
+                  <c:v>6.3125913973947076</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8.820258898030108</c:v>
+                  <c:v>7.5114752171370842</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6.794356996267517</c:v>
+                  <c:v>6.591099408051651</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>13.085290037842814</c:v>
+                  <c:v>10.302194305399103</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>9.5542382804923562</c:v>
+                  <c:v>11.500108755597664</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>10.165636019884383</c:v>
+                  <c:v>11.797490681589681</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>14.884347488358706</c:v>
+                  <c:v>14.436612034540406</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>16.448102799094741</c:v>
+                  <c:v>11.543588910604143</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>15.69630373126359</c:v>
+                  <c:v>13.350651208017116</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>16.177382142751551</c:v>
+                  <c:v>13.146016456868958</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>16.07878941680298</c:v>
+                  <c:v>16.160927795197807</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>17.471696072041642</c:v>
+                  <c:v>13.631394328112865</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>13.679708813525982</c:v>
+                  <c:v>15.15335953948777</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2313,16 +2316,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>280147</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>100107</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>444499</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>97118</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>705970</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>19424</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>41088</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>71719</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2349,16 +2352,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>287620</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>414619</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>107577</xdr:rowOff>
+      <xdr:rowOff>100107</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>713443</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>26895</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>11208</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>37353</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2703,10 +2706,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E49B87-C84A-2142-A99F-5E2EBBD232E0}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2725,8 +2728,11 @@
       <c r="H1" t="s">
         <v>3</v>
       </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2738,17 +2744,21 @@
       </c>
       <c r="D2" s="1">
         <f ca="1">2+1.2*B2+_xlfn.NORM.INV(RAND(),0,2)</f>
-        <v>7.31646909511724</v>
+        <v>4.3746426426433738</v>
       </c>
       <c r="E2">
-        <v>30.200000000000003</v>
+        <v>27.200000000000003</v>
       </c>
       <c r="H2">
         <f>_xlfn.STDEV.S(E2:E8)</f>
-        <v>3.0873011792548812</v>
+        <v>3.0873011792549137</v>
+      </c>
+      <c r="I2">
+        <f>AVERAGE(E2:E8)</f>
+        <v>25.485714285714288</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2760,17 +2770,21 @@
       </c>
       <c r="D3" s="1">
         <f t="shared" ref="D3:D22" ca="1" si="0">2+1.2*B3+_xlfn.NORM.INV(RAND(),0,2)</f>
-        <v>5.7218827786121809</v>
+        <v>5.5008606877370481</v>
       </c>
       <c r="E3">
-        <v>31.200000000000003</v>
+        <v>28.200000000000003</v>
       </c>
       <c r="H3">
         <f>_xlfn.STDEV.S(E9:E15)</f>
-        <v>2.1187372699434817</v>
+        <v>1.9336617126704347</v>
+      </c>
+      <c r="I3">
+        <f>AVERAGE(E9:E15)</f>
+        <v>15.02857142857143</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2782,17 +2796,21 @@
       </c>
       <c r="D4" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>7.0030834451737736</v>
+        <v>6.728532060884449</v>
       </c>
       <c r="E4">
-        <v>27.6</v>
+        <v>24.6</v>
       </c>
       <c r="H4">
         <f>_xlfn.STDEV.S(E16:E22)</f>
         <v>5.0164491330783116</v>
       </c>
+      <c r="I4">
+        <f>AVERAGE(E16:E22)</f>
+        <v>31.11428571428571</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2804,13 +2822,13 @@
       </c>
       <c r="D5" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.7373257292292248</v>
+        <v>7.4244846225858225</v>
       </c>
       <c r="E5">
-        <v>24.4</v>
+        <v>21.4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2822,13 +2840,13 @@
       </c>
       <c r="D6" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>4.2317284424398309</v>
+        <v>7.2868256008981298</v>
       </c>
       <c r="E6">
-        <v>29.200000000000003</v>
+        <v>26.200000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2840,13 +2858,13 @@
       </c>
       <c r="D7" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>1.5552895628505508</v>
+        <v>1.0148031525997094</v>
       </c>
       <c r="E7">
-        <v>32.200000000000003</v>
+        <v>29.200000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2858,13 +2876,13 @@
       </c>
       <c r="D8" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.1154018411183682</v>
+        <v>6.3401554116243615</v>
       </c>
       <c r="E8">
-        <v>24.6</v>
+        <v>21.6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2876,13 +2894,13 @@
       </c>
       <c r="D9" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.0783389461155526</v>
+        <v>8.8722619994024718</v>
       </c>
       <c r="E9">
         <v>14.2</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2894,13 +2912,13 @@
       </c>
       <c r="D10" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.9269373449618037</v>
+        <v>6.3125913973947076</v>
       </c>
       <c r="E10">
-        <v>17.3</v>
+        <v>15.2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2912,13 +2930,13 @@
       </c>
       <c r="D11" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>8.820258898030108</v>
+        <v>7.5114752171370842</v>
       </c>
       <c r="E11">
         <v>13.100000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2930,13 +2948,13 @@
       </c>
       <c r="D12" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>6.794356996267517</v>
+        <v>6.591099408051651</v>
       </c>
       <c r="E12">
         <v>14.100000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2948,13 +2966,13 @@
       </c>
       <c r="D13" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.085290037842814</v>
+        <v>10.302194305399103</v>
       </c>
       <c r="E13">
         <v>14.3</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2966,13 +2984,13 @@
       </c>
       <c r="D14" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>9.5542382804923562</v>
+        <v>11.500108755597664</v>
       </c>
       <c r="E14">
         <v>15.2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2984,13 +3002,13 @@
       </c>
       <c r="D15" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>10.165636019884383</v>
+        <v>11.797490681589681</v>
       </c>
       <c r="E15">
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3002,7 +3020,7 @@
       </c>
       <c r="D16" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>14.884347488358706</v>
+        <v>14.436612034540406</v>
       </c>
       <c r="E16">
         <v>27.6</v>
@@ -3020,7 +3038,7 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.448102799094741</v>
+        <v>11.543588910604143</v>
       </c>
       <c r="E17">
         <v>22.2</v>
@@ -3038,7 +3056,7 @@
       </c>
       <c r="D18" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>15.69630373126359</v>
+        <v>13.350651208017116</v>
       </c>
       <c r="E18">
         <v>35.1</v>
@@ -3056,7 +3074,7 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.177382142751551</v>
+        <v>13.146016456868958</v>
       </c>
       <c r="E19">
         <v>32.4</v>
@@ -3074,7 +3092,7 @@
       </c>
       <c r="D20" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>16.07878941680298</v>
+        <v>16.160927795197807</v>
       </c>
       <c r="E20">
         <v>37.1</v>
@@ -3092,7 +3110,7 @@
       </c>
       <c r="D21" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>17.471696072041642</v>
+        <v>13.631394328112865</v>
       </c>
       <c r="E21">
         <v>33.299999999999997</v>
@@ -3110,7 +3128,7 @@
       </c>
       <c r="D22" s="1">
         <f t="shared" ca="1" si="0"/>
-        <v>13.679708813525982</v>
+        <v>15.15335953948777</v>
       </c>
       <c r="E22">
         <v>30.1</v>
